--- a/docs/downloads/04/tbl_cm_act_sex_alaotra_tous.xlsx
+++ b/docs/downloads/04/tbl_cm_act_sex_alaotra_tous.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E73"/>
+  <dimension ref="A1:E92"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -394,14 +394,8 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Cultivateur</t>
-        </is>
-      </c>
-      <c r="D2">
-        <v>2</v>
-      </c>
-      <c r="E2">
-        <v>100</v>
+          <t>Cultivateur exploitant</t>
+        </is>
       </c>
     </row>
     <row r="3">
@@ -417,14 +411,8 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Autres</t>
-        </is>
-      </c>
-      <c r="D3">
-        <v>4</v>
-      </c>
-      <c r="E3">
-        <v>13.8</v>
+          <t>Commerce &amp; Restauration</t>
+        </is>
       </c>
     </row>
     <row r="4">
@@ -440,14 +428,14 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Commerçant</t>
+          <t>Cultivateur exploitant</t>
         </is>
       </c>
       <c r="D4">
-        <v>1</v>
+        <v>22</v>
       </c>
       <c r="E4">
-        <v>3.4</v>
+        <v>75.90000000000001</v>
       </c>
     </row>
     <row r="5">
@@ -463,37 +451,31 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Cultivateur</t>
+          <t>Elevage, Pêche &amp; Ress. nat.</t>
         </is>
       </c>
       <c r="D5">
-        <v>22</v>
+        <v>6</v>
       </c>
       <c r="E5">
-        <v>75.90000000000001</v>
+        <v>20.7</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Alaotra - Ambatoharanana</t>
+          <t>Alaotra - Ambatomanga</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Homme</t>
+          <t>Femme</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Éleveur</t>
-        </is>
-      </c>
-      <c r="D6">
-        <v>2</v>
-      </c>
-      <c r="E6">
-        <v>6.9</v>
+          <t>Commerce &amp; Restauration</t>
+        </is>
       </c>
     </row>
     <row r="7">
@@ -509,14 +491,8 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Autres</t>
-        </is>
-      </c>
-      <c r="D7">
-        <v>4</v>
-      </c>
-      <c r="E7">
-        <v>36.4</v>
+          <t>Cultivateur exploitant</t>
+        </is>
       </c>
     </row>
     <row r="8">
@@ -532,14 +508,8 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Commerçant</t>
-        </is>
-      </c>
-      <c r="D8">
-        <v>4</v>
-      </c>
-      <c r="E8">
-        <v>36.4</v>
+          <t>Ouvrier agricole</t>
+        </is>
       </c>
     </row>
     <row r="9">
@@ -555,14 +525,8 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Cultivateur</t>
-        </is>
-      </c>
-      <c r="D9">
-        <v>2</v>
-      </c>
-      <c r="E9">
-        <v>18.2</v>
+          <t>Services &amp; Autres</t>
+        </is>
       </c>
     </row>
     <row r="10">
@@ -573,19 +537,19 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Femme</t>
+          <t>Homme</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Ouvrier agricole</t>
+          <t>Artisanat, BTP &amp; Transport</t>
         </is>
       </c>
       <c r="D10">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="E10">
-        <v>9.1</v>
+        <v>23.2</v>
       </c>
     </row>
     <row r="11">
@@ -601,14 +565,8 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Autres</t>
-        </is>
-      </c>
-      <c r="D11">
-        <v>21</v>
-      </c>
-      <c r="E11">
-        <v>36.8</v>
+          <t>Commerce &amp; Restauration</t>
+        </is>
       </c>
     </row>
     <row r="12">
@@ -624,14 +582,14 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Commerçant</t>
+          <t>Cultivateur exploitant</t>
         </is>
       </c>
       <c r="D12">
-        <v>1</v>
+        <v>18</v>
       </c>
       <c r="E12">
-        <v>1.8</v>
+        <v>32.1</v>
       </c>
     </row>
     <row r="13">
@@ -647,14 +605,8 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Cultivateur</t>
-        </is>
-      </c>
-      <c r="D13">
-        <v>18</v>
-      </c>
-      <c r="E13">
-        <v>31.6</v>
+          <t>Elevage, Pêche &amp; Ress. nat.</t>
+        </is>
       </c>
     </row>
     <row r="14">
@@ -677,7 +629,7 @@
         <v>16</v>
       </c>
       <c r="E14">
-        <v>28.1</v>
+        <v>28.6</v>
       </c>
     </row>
     <row r="15">
@@ -693,14 +645,14 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Éleveur</t>
+          <t>Services &amp; Autres</t>
         </is>
       </c>
       <c r="D15">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E15">
-        <v>1.8</v>
+        <v>8.9</v>
       </c>
     </row>
     <row r="16">
@@ -716,14 +668,8 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Autres</t>
-        </is>
-      </c>
-      <c r="D16">
-        <v>8</v>
-      </c>
-      <c r="E16">
-        <v>47.1</v>
+          <t>Artisanat, BTP &amp; Transport</t>
+        </is>
       </c>
     </row>
     <row r="17">
@@ -739,14 +685,8 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Cultivateur</t>
-        </is>
-      </c>
-      <c r="D17">
-        <v>7</v>
-      </c>
-      <c r="E17">
-        <v>41.2</v>
+          <t>Commerce &amp; Restauration</t>
+        </is>
       </c>
     </row>
     <row r="18">
@@ -762,14 +702,14 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Ouvrier agricole</t>
+          <t>Cultivateur exploitant</t>
         </is>
       </c>
       <c r="D18">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="E18">
-        <v>11.8</v>
+        <v>41.2</v>
       </c>
     </row>
     <row r="19">
@@ -780,19 +720,13 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Homme</t>
+          <t>Femme</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Autres</t>
-        </is>
-      </c>
-      <c r="D19">
-        <v>5</v>
-      </c>
-      <c r="E19">
-        <v>12.2</v>
+          <t>Ouvrier agricole</t>
+        </is>
       </c>
     </row>
     <row r="20">
@@ -803,19 +737,13 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Homme</t>
+          <t>Femme</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Commerçant</t>
-        </is>
-      </c>
-      <c r="D20">
-        <v>1</v>
-      </c>
-      <c r="E20">
-        <v>2.4</v>
+          <t>Services &amp; Autres</t>
+        </is>
       </c>
     </row>
     <row r="21">
@@ -831,14 +759,8 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Cultivateur</t>
-        </is>
-      </c>
-      <c r="D21">
-        <v>31</v>
-      </c>
-      <c r="E21">
-        <v>75.59999999999999</v>
+          <t>Artisanat, BTP &amp; Transport</t>
+        </is>
       </c>
     </row>
     <row r="22">
@@ -854,83 +776,65 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Ouvrier agricole</t>
-        </is>
-      </c>
-      <c r="D22">
-        <v>4</v>
-      </c>
-      <c r="E22">
-        <v>9.800000000000001</v>
+          <t>Commerce &amp; Restauration</t>
+        </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Alaotra - Ambohidrony</t>
+          <t>Alaotra - Ambodivoara</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Femme</t>
+          <t>Homme</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Autres</t>
+          <t>Cultivateur exploitant</t>
         </is>
       </c>
       <c r="D23">
-        <v>6</v>
+        <v>31</v>
       </c>
       <c r="E23">
-        <v>42.9</v>
+        <v>75.59999999999999</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Alaotra - Ambohidrony</t>
+          <t>Alaotra - Ambodivoara</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Femme</t>
+          <t>Homme</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Commerçant</t>
-        </is>
-      </c>
-      <c r="D24">
-        <v>2</v>
-      </c>
-      <c r="E24">
-        <v>14.3</v>
+          <t>Elevage, Pêche &amp; Ress. nat.</t>
+        </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Alaotra - Ambohidrony</t>
+          <t>Alaotra - Ambodivoara</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Femme</t>
+          <t>Homme</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Cultivateur</t>
-        </is>
-      </c>
-      <c r="D25">
-        <v>3</v>
-      </c>
-      <c r="E25">
-        <v>21.4</v>
+          <t>Ouvrier agricole</t>
+        </is>
       </c>
     </row>
     <row r="26">
@@ -946,14 +850,8 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Ouvrier agricole</t>
-        </is>
-      </c>
-      <c r="D26">
-        <v>3</v>
-      </c>
-      <c r="E26">
-        <v>21.4</v>
+          <t>Artisanat, BTP &amp; Transport</t>
+        </is>
       </c>
     </row>
     <row r="27">
@@ -964,19 +862,13 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Homme</t>
+          <t>Femme</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Autres</t>
-        </is>
-      </c>
-      <c r="D27">
-        <v>10</v>
-      </c>
-      <c r="E27">
-        <v>26.3</v>
+          <t>Commerce &amp; Restauration</t>
+        </is>
       </c>
     </row>
     <row r="28">
@@ -987,19 +879,13 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Homme</t>
+          <t>Femme</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Commerçant</t>
-        </is>
-      </c>
-      <c r="D28">
-        <v>1</v>
-      </c>
-      <c r="E28">
-        <v>2.6</v>
+          <t>Cultivateur exploitant</t>
+        </is>
       </c>
     </row>
     <row r="29">
@@ -1010,19 +896,13 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Homme</t>
+          <t>Femme</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Cultivateur</t>
-        </is>
-      </c>
-      <c r="D29">
-        <v>16</v>
-      </c>
-      <c r="E29">
-        <v>42.1</v>
+          <t>Elevage, Pêche &amp; Ress. nat.</t>
+        </is>
       </c>
     </row>
     <row r="30">
@@ -1033,25 +913,19 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Homme</t>
+          <t>Femme</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
           <t>Ouvrier agricole</t>
         </is>
-      </c>
-      <c r="D30">
-        <v>11</v>
-      </c>
-      <c r="E30">
-        <v>28.9</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Alaotra - Analamiranga</t>
+          <t>Alaotra - Ambohidrony</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1061,89 +935,77 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Autres</t>
-        </is>
-      </c>
-      <c r="D31">
-        <v>5</v>
-      </c>
-      <c r="E31">
-        <v>50</v>
+          <t>Services &amp; Autres</t>
+        </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Alaotra - Analamiranga</t>
+          <t>Alaotra - Ambohidrony</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Femme</t>
+          <t>Homme</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Commerçant</t>
+          <t>Artisanat, BTP &amp; Transport</t>
         </is>
       </c>
       <c r="D32">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E32">
-        <v>20</v>
+        <v>13.2</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Alaotra - Analamiranga</t>
+          <t>Alaotra - Ambohidrony</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Femme</t>
+          <t>Homme</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Cultivateur</t>
-        </is>
-      </c>
-      <c r="D33">
-        <v>2</v>
-      </c>
-      <c r="E33">
-        <v>20</v>
+          <t>Commerce &amp; Restauration</t>
+        </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Alaotra - Analamiranga</t>
+          <t>Alaotra - Ambohidrony</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Femme</t>
+          <t>Homme</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Ouvrier agricole</t>
+          <t>Cultivateur exploitant</t>
         </is>
       </c>
       <c r="D34">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="E34">
-        <v>10</v>
+        <v>42.1</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Alaotra - Analamiranga</t>
+          <t>Alaotra - Ambohidrony</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1153,20 +1015,20 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Autres</t>
+          <t>Elevage, Pêche &amp; Ress. nat.</t>
         </is>
       </c>
       <c r="D35">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E35">
-        <v>11.1</v>
+        <v>13.2</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Alaotra - Analamiranga</t>
+          <t>Alaotra - Ambohidrony</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1176,14 +1038,14 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Commerçant</t>
+          <t>Ouvrier agricole</t>
         </is>
       </c>
       <c r="D36">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="E36">
-        <v>2.8</v>
+        <v>28.9</v>
       </c>
     </row>
     <row r="37">
@@ -1194,19 +1056,13 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Homme</t>
+          <t>Femme</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Cultivateur</t>
-        </is>
-      </c>
-      <c r="D37">
-        <v>26</v>
-      </c>
-      <c r="E37">
-        <v>72.2</v>
+          <t>Artisanat, BTP &amp; Transport</t>
+        </is>
       </c>
     </row>
     <row r="38">
@@ -1217,25 +1073,19 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Homme</t>
+          <t>Femme</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Ouvrier agricole</t>
-        </is>
-      </c>
-      <c r="D38">
-        <v>5</v>
-      </c>
-      <c r="E38">
-        <v>13.9</v>
+          <t>Commerce &amp; Restauration</t>
+        </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Alaotra - Avaradrano</t>
+          <t>Alaotra - Analamiranga</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1245,20 +1095,14 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Autres</t>
-        </is>
-      </c>
-      <c r="D39">
-        <v>6</v>
-      </c>
-      <c r="E39">
-        <v>27.3</v>
+          <t>Cultivateur exploitant</t>
+        </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Alaotra - Avaradrano</t>
+          <t>Alaotra - Analamiranga</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1268,20 +1112,14 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Commerçant</t>
-        </is>
-      </c>
-      <c r="D40">
-        <v>1</v>
-      </c>
-      <c r="E40">
-        <v>4.5</v>
+          <t>Ouvrier agricole</t>
+        </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Alaotra - Avaradrano</t>
+          <t>Alaotra - Analamiranga</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1291,66 +1129,48 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Cultivateur</t>
-        </is>
-      </c>
-      <c r="D41">
-        <v>13</v>
-      </c>
-      <c r="E41">
-        <v>59.1</v>
+          <t>Services &amp; Autres</t>
+        </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Alaotra - Avaradrano</t>
+          <t>Alaotra - Analamiranga</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Femme</t>
+          <t>Homme</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Ouvrier agricole</t>
-        </is>
-      </c>
-      <c r="D42">
-        <v>1</v>
-      </c>
-      <c r="E42">
-        <v>4.5</v>
+          <t>Artisanat, BTP &amp; Transport</t>
+        </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Alaotra - Avaradrano</t>
+          <t>Alaotra - Analamiranga</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Femme</t>
+          <t>Homme</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Éleveur</t>
-        </is>
-      </c>
-      <c r="D43">
-        <v>1</v>
-      </c>
-      <c r="E43">
-        <v>4.5</v>
+          <t>Commerce &amp; Restauration</t>
+        </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Alaotra - Avaradrano</t>
+          <t>Alaotra - Analamiranga</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -1360,20 +1180,20 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Autres</t>
+          <t>Cultivateur exploitant</t>
         </is>
       </c>
       <c r="D44">
-        <v>14</v>
+        <v>26</v>
       </c>
       <c r="E44">
-        <v>20.6</v>
+        <v>72.2</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Alaotra - Avaradrano</t>
+          <t>Alaotra - Analamiranga</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -1383,20 +1203,20 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Commerçant</t>
+          <t>Ouvrier agricole</t>
         </is>
       </c>
       <c r="D45">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E45">
-        <v>1.5</v>
+        <v>13.9</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Alaotra - Avaradrano</t>
+          <t>Alaotra - Analamiranga</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -1406,14 +1226,8 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Cultivateur</t>
-        </is>
-      </c>
-      <c r="D46">
-        <v>52</v>
-      </c>
-      <c r="E46">
-        <v>76.5</v>
+          <t>Services &amp; Autres</t>
+        </is>
       </c>
     </row>
     <row r="47">
@@ -1424,25 +1238,19 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Homme</t>
+          <t>Femme</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Ouvrier agricole</t>
-        </is>
-      </c>
-      <c r="D47">
-        <v>1</v>
-      </c>
-      <c r="E47">
-        <v>1.5</v>
+          <t>Artisanat, BTP &amp; Transport</t>
+        </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Alaotra - Feramanga Atsimo</t>
+          <t>Alaotra - Avaradrano</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -1452,20 +1260,14 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Autres</t>
-        </is>
-      </c>
-      <c r="D48">
-        <v>4</v>
-      </c>
-      <c r="E48">
-        <v>26.7</v>
+          <t>Commerce &amp; Restauration</t>
+        </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Alaotra - Feramanga Atsimo</t>
+          <t>Alaotra - Avaradrano</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -1475,20 +1277,20 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Commerçant</t>
+          <t>Cultivateur exploitant</t>
         </is>
       </c>
       <c r="D49">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="E49">
-        <v>13.3</v>
+        <v>61.9</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Alaotra - Feramanga Atsimo</t>
+          <t>Alaotra - Avaradrano</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -1498,20 +1300,14 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Cultivateur</t>
-        </is>
-      </c>
-      <c r="D50">
-        <v>7</v>
-      </c>
-      <c r="E50">
-        <v>46.7</v>
+          <t>Elevage, Pêche &amp; Ress. nat.</t>
+        </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Alaotra - Feramanga Atsimo</t>
+          <t>Alaotra - Avaradrano</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -1523,18 +1319,12 @@
         <is>
           <t>Ouvrier agricole</t>
         </is>
-      </c>
-      <c r="D51">
-        <v>1</v>
-      </c>
-      <c r="E51">
-        <v>6.7</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Alaotra - Feramanga Atsimo</t>
+          <t>Alaotra - Avaradrano</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -1544,20 +1334,14 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Éleveur</t>
-        </is>
-      </c>
-      <c r="D52">
-        <v>1</v>
-      </c>
-      <c r="E52">
-        <v>6.7</v>
+          <t>Services &amp; Autres</t>
+        </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Alaotra - Feramanga Atsimo</t>
+          <t>Alaotra - Avaradrano</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -1567,20 +1351,20 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Autres</t>
+          <t>Artisanat, BTP &amp; Transport</t>
         </is>
       </c>
       <c r="D53">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E53">
-        <v>13.5</v>
+        <v>7.4</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Alaotra - Feramanga Atsimo</t>
+          <t>Alaotra - Avaradrano</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -1590,20 +1374,14 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Commerçant</t>
-        </is>
-      </c>
-      <c r="D54">
-        <v>2</v>
-      </c>
-      <c r="E54">
-        <v>2.7</v>
+          <t>Commerce &amp; Restauration</t>
+        </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Alaotra - Feramanga Atsimo</t>
+          <t>Alaotra - Avaradrano</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -1613,20 +1391,20 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Cultivateur</t>
+          <t>Cultivateur exploitant</t>
         </is>
       </c>
       <c r="D55">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E55">
-        <v>71.59999999999999</v>
+        <v>76.5</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Alaotra - Feramanga Atsimo</t>
+          <t>Alaotra - Avaradrano</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -1636,66 +1414,48 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Ouvrier agricole</t>
-        </is>
-      </c>
-      <c r="D56">
-        <v>9</v>
-      </c>
-      <c r="E56">
-        <v>12.2</v>
+          <t>Elevage, Pêche &amp; Ress. nat.</t>
+        </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Alaotra - Mangabe</t>
+          <t>Alaotra - Avaradrano</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Femme</t>
+          <t>Homme</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Autres</t>
-        </is>
-      </c>
-      <c r="D57">
-        <v>3</v>
-      </c>
-      <c r="E57">
-        <v>15.8</v>
+          <t>Ouvrier agricole</t>
+        </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Alaotra - Mangabe</t>
+          <t>Alaotra - Avaradrano</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Femme</t>
+          <t>Homme</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Commerçant</t>
-        </is>
-      </c>
-      <c r="D58">
-        <v>2</v>
-      </c>
-      <c r="E58">
-        <v>10.5</v>
+          <t>Services &amp; Autres</t>
+        </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Alaotra - Mangabe</t>
+          <t>Alaotra - Feramanga Atsimo</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -1705,20 +1465,14 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Cultivateur</t>
-        </is>
-      </c>
-      <c r="D59">
-        <v>10</v>
-      </c>
-      <c r="E59">
-        <v>52.6</v>
+          <t>Artisanat, BTP &amp; Transport</t>
+        </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Alaotra - Mangabe</t>
+          <t>Alaotra - Feramanga Atsimo</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -1728,204 +1482,168 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Ouvrier agricole</t>
-        </is>
-      </c>
-      <c r="D60">
-        <v>4</v>
-      </c>
-      <c r="E60">
-        <v>21.1</v>
+          <t>Commerce &amp; Restauration</t>
+        </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Alaotra - Mangabe</t>
+          <t>Alaotra - Feramanga Atsimo</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Homme</t>
+          <t>Femme</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Autres</t>
+          <t>Cultivateur exploitant</t>
         </is>
       </c>
       <c r="D61">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E61">
-        <v>16.7</v>
+        <v>46.7</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Alaotra - Mangabe</t>
+          <t>Alaotra - Feramanga Atsimo</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Homme</t>
+          <t>Femme</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Cultivateur</t>
-        </is>
-      </c>
-      <c r="D62">
-        <v>41</v>
-      </c>
-      <c r="E62">
-        <v>75.90000000000001</v>
+          <t>Elevage, Pêche &amp; Ress. nat.</t>
+        </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Alaotra - Mangabe</t>
+          <t>Alaotra - Feramanga Atsimo</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Homme</t>
+          <t>Femme</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
           <t>Ouvrier agricole</t>
         </is>
-      </c>
-      <c r="D63">
-        <v>4</v>
-      </c>
-      <c r="E63">
-        <v>7.4</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Alaotra - Tous</t>
+          <t>Alaotra - Feramanga Atsimo</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Femme</t>
+          <t>Homme</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Autres</t>
-        </is>
-      </c>
-      <c r="D64">
-        <v>36</v>
-      </c>
-      <c r="E64">
-        <v>32.7</v>
+          <t>Artisanat, BTP &amp; Transport</t>
+        </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Alaotra - Tous</t>
+          <t>Alaotra - Feramanga Atsimo</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Femme</t>
+          <t>Homme</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Commerçant</t>
-        </is>
-      </c>
-      <c r="D65">
-        <v>13</v>
-      </c>
-      <c r="E65">
-        <v>11.8</v>
+          <t>Commerce &amp; Restauration</t>
+        </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Alaotra - Tous</t>
+          <t>Alaotra - Feramanga Atsimo</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Femme</t>
+          <t>Homme</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Cultivateur</t>
+          <t>Cultivateur exploitant</t>
         </is>
       </c>
       <c r="D66">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="E66">
-        <v>41.8</v>
+        <v>71.59999999999999</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Alaotra - Tous</t>
+          <t>Alaotra - Feramanga Atsimo</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Femme</t>
+          <t>Homme</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Ouvrier agricole</t>
-        </is>
-      </c>
-      <c r="D67">
-        <v>13</v>
-      </c>
-      <c r="E67">
-        <v>11.8</v>
+          <t>Elevage, Pêche &amp; Ress. nat.</t>
+        </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Alaotra - Tous</t>
+          <t>Alaotra - Feramanga Atsimo</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Femme</t>
+          <t>Homme</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Éleveur</t>
+          <t>Ouvrier agricole</t>
         </is>
       </c>
       <c r="D68">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="E68">
-        <v>1.8</v>
+        <v>12.2</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Alaotra - Tous</t>
+          <t>Alaotra - Feramanga Atsimo</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -1935,106 +1653,483 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Autres</t>
-        </is>
-      </c>
-      <c r="D69">
-        <v>77</v>
-      </c>
-      <c r="E69">
-        <v>19.4</v>
+          <t>Services &amp; Autres</t>
+        </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Alaotra - Tous</t>
+          <t>Alaotra - Mangabe</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Homme</t>
+          <t>Femme</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Commerçant</t>
-        </is>
-      </c>
-      <c r="D70">
-        <v>8</v>
-      </c>
-      <c r="E70">
-        <v>2</v>
+          <t>Artisanat, BTP &amp; Transport</t>
+        </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Alaotra - Tous</t>
+          <t>Alaotra - Mangabe</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Homme</t>
+          <t>Femme</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Cultivateur</t>
-        </is>
-      </c>
-      <c r="D71">
-        <v>259</v>
-      </c>
-      <c r="E71">
-        <v>65.2</v>
+          <t>Commerce &amp; Restauration</t>
+        </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Alaotra - Tous</t>
+          <t>Alaotra - Mangabe</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Homme</t>
+          <t>Femme</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Ouvrier agricole</t>
+          <t>Cultivateur exploitant</t>
         </is>
       </c>
       <c r="D72">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="E72">
-        <v>12.6</v>
+        <v>52.6</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
+          <t>Alaotra - Mangabe</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>Femme</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>Elevage, Pêche &amp; Ress. nat.</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>Alaotra - Mangabe</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>Femme</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>Ouvrier agricole</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>Alaotra - Mangabe</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>Femme</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>Services &amp; Autres</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>Alaotra - Mangabe</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>Homme</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>Artisanat, BTP &amp; Transport</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>Alaotra - Mangabe</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>Homme</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>Cultivateur exploitant</t>
+        </is>
+      </c>
+      <c r="D77">
+        <v>41</v>
+      </c>
+      <c r="E77">
+        <v>75.90000000000001</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>Alaotra - Mangabe</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>Homme</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>Elevage, Pêche &amp; Ress. nat.</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>Alaotra - Mangabe</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>Homme</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>Ouvrier agricole</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>Alaotra - Mangabe</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>Homme</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>Services &amp; Autres</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
           <t>Alaotra - Tous</t>
         </is>
       </c>
-      <c r="B73" t="inlineStr">
-        <is>
-          <t>Homme</t>
-        </is>
-      </c>
-      <c r="C73" t="inlineStr">
-        <is>
-          <t>Éleveur</t>
-        </is>
-      </c>
-      <c r="D73">
-        <v>3</v>
-      </c>
-      <c r="E73">
-        <v>0.8</v>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>Femme</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>Artisanat, BTP &amp; Transport</t>
+        </is>
+      </c>
+      <c r="D81">
+        <v>8</v>
+      </c>
+      <c r="E81">
+        <v>7.3</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>Alaotra - Tous</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>Femme</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>Commerce &amp; Restauration</t>
+        </is>
+      </c>
+      <c r="D82">
+        <v>18</v>
+      </c>
+      <c r="E82">
+        <v>16.5</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>Alaotra - Tous</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>Femme</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>Cultivateur exploitant</t>
+        </is>
+      </c>
+      <c r="D83">
+        <v>46</v>
+      </c>
+      <c r="E83">
+        <v>42.2</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>Alaotra - Tous</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>Femme</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>Elevage, Pêche &amp; Ress. nat.</t>
+        </is>
+      </c>
+      <c r="D84">
+        <v>6</v>
+      </c>
+      <c r="E84">
+        <v>5.5</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>Alaotra - Tous</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>Femme</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>Ouvrier agricole</t>
+        </is>
+      </c>
+      <c r="D85">
+        <v>13</v>
+      </c>
+      <c r="E85">
+        <v>11.9</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>Alaotra - Tous</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>Femme</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>Services &amp; Autres</t>
+        </is>
+      </c>
+      <c r="D86">
+        <v>18</v>
+      </c>
+      <c r="E86">
+        <v>16.5</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>Alaotra - Tous</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>Homme</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>Artisanat, BTP &amp; Transport</t>
+        </is>
+      </c>
+      <c r="D87">
+        <v>37</v>
+      </c>
+      <c r="E87">
+        <v>9.300000000000001</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>Alaotra - Tous</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>Homme</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>Commerce &amp; Restauration</t>
+        </is>
+      </c>
+      <c r="D88">
+        <v>10</v>
+      </c>
+      <c r="E88">
+        <v>2.5</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>Alaotra - Tous</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>Homme</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>Cultivateur exploitant</t>
+        </is>
+      </c>
+      <c r="D89">
+        <v>259</v>
+      </c>
+      <c r="E89">
+        <v>65.40000000000001</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>Alaotra - Tous</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>Homme</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>Elevage, Pêche &amp; Ress. nat.</t>
+        </is>
+      </c>
+      <c r="D90">
+        <v>25</v>
+      </c>
+      <c r="E90">
+        <v>6.3</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>Alaotra - Tous</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>Homme</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>Ouvrier agricole</t>
+        </is>
+      </c>
+      <c r="D91">
+        <v>50</v>
+      </c>
+      <c r="E91">
+        <v>12.6</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>Alaotra - Tous</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>Homme</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>Services &amp; Autres</t>
+        </is>
+      </c>
+      <c r="D92">
+        <v>15</v>
+      </c>
+      <c r="E92">
+        <v>3.8</v>
       </c>
     </row>
   </sheetData>

--- a/docs/downloads/04/tbl_cm_act_sex_alaotra_tous.xlsx
+++ b/docs/downloads/04/tbl_cm_act_sex_alaotra_tous.xlsx
@@ -384,7 +384,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Alaotra - Ambatoharanana</t>
+          <t>Ambatoharanana</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -401,7 +401,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Alaotra - Ambatoharanana</t>
+          <t>Ambatoharanana</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -418,7 +418,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Alaotra - Ambatoharanana</t>
+          <t>Ambatoharanana</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -441,7 +441,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Alaotra - Ambatoharanana</t>
+          <t>Ambatoharanana</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -464,7 +464,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Alaotra - Ambatomanga</t>
+          <t>Ambatomanga</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -481,7 +481,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Alaotra - Ambatomanga</t>
+          <t>Ambatomanga</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -498,7 +498,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Alaotra - Ambatomanga</t>
+          <t>Ambatomanga</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -515,7 +515,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Alaotra - Ambatomanga</t>
+          <t>Ambatomanga</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -532,7 +532,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Alaotra - Ambatomanga</t>
+          <t>Ambatomanga</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -555,7 +555,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Alaotra - Ambatomanga</t>
+          <t>Ambatomanga</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -572,7 +572,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Alaotra - Ambatomanga</t>
+          <t>Ambatomanga</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -595,7 +595,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Alaotra - Ambatomanga</t>
+          <t>Ambatomanga</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -612,7 +612,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Alaotra - Ambatomanga</t>
+          <t>Ambatomanga</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -635,7 +635,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Alaotra - Ambatomanga</t>
+          <t>Ambatomanga</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -658,7 +658,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Alaotra - Ambodivoara</t>
+          <t>Ambodivoara</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -675,7 +675,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Alaotra - Ambodivoara</t>
+          <t>Ambodivoara</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -692,7 +692,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Alaotra - Ambodivoara</t>
+          <t>Ambodivoara</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -715,7 +715,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Alaotra - Ambodivoara</t>
+          <t>Ambodivoara</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -732,7 +732,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Alaotra - Ambodivoara</t>
+          <t>Ambodivoara</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -749,7 +749,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Alaotra - Ambodivoara</t>
+          <t>Ambodivoara</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -766,7 +766,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Alaotra - Ambodivoara</t>
+          <t>Ambodivoara</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -783,7 +783,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Alaotra - Ambodivoara</t>
+          <t>Ambodivoara</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -806,7 +806,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Alaotra - Ambodivoara</t>
+          <t>Ambodivoara</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -823,7 +823,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Alaotra - Ambodivoara</t>
+          <t>Ambodivoara</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -840,7 +840,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Alaotra - Ambohidrony</t>
+          <t>Ambohidrony</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -857,7 +857,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Alaotra - Ambohidrony</t>
+          <t>Ambohidrony</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -874,7 +874,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Alaotra - Ambohidrony</t>
+          <t>Ambohidrony</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -891,7 +891,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Alaotra - Ambohidrony</t>
+          <t>Ambohidrony</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -908,7 +908,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Alaotra - Ambohidrony</t>
+          <t>Ambohidrony</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -925,7 +925,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Alaotra - Ambohidrony</t>
+          <t>Ambohidrony</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -942,7 +942,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Alaotra - Ambohidrony</t>
+          <t>Ambohidrony</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -965,7 +965,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Alaotra - Ambohidrony</t>
+          <t>Ambohidrony</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -982,7 +982,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Alaotra - Ambohidrony</t>
+          <t>Ambohidrony</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1005,7 +1005,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Alaotra - Ambohidrony</t>
+          <t>Ambohidrony</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1028,7 +1028,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Alaotra - Ambohidrony</t>
+          <t>Ambohidrony</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1051,7 +1051,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Alaotra - Analamiranga</t>
+          <t>Analamiranga</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1068,7 +1068,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Alaotra - Analamiranga</t>
+          <t>Analamiranga</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1085,7 +1085,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Alaotra - Analamiranga</t>
+          <t>Analamiranga</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1102,7 +1102,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Alaotra - Analamiranga</t>
+          <t>Analamiranga</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1119,7 +1119,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Alaotra - Analamiranga</t>
+          <t>Analamiranga</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1136,7 +1136,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Alaotra - Analamiranga</t>
+          <t>Analamiranga</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -1153,7 +1153,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Alaotra - Analamiranga</t>
+          <t>Analamiranga</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -1170,7 +1170,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Alaotra - Analamiranga</t>
+          <t>Analamiranga</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -1193,7 +1193,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Alaotra - Analamiranga</t>
+          <t>Analamiranga</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -1216,7 +1216,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Alaotra - Analamiranga</t>
+          <t>Analamiranga</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -1233,7 +1233,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Alaotra - Avaradrano</t>
+          <t>Avaradrano</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -1250,7 +1250,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Alaotra - Avaradrano</t>
+          <t>Avaradrano</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -1267,7 +1267,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Alaotra - Avaradrano</t>
+          <t>Avaradrano</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -1290,7 +1290,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Alaotra - Avaradrano</t>
+          <t>Avaradrano</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -1307,7 +1307,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Alaotra - Avaradrano</t>
+          <t>Avaradrano</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -1324,7 +1324,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Alaotra - Avaradrano</t>
+          <t>Avaradrano</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -1341,7 +1341,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Alaotra - Avaradrano</t>
+          <t>Avaradrano</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -1364,7 +1364,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Alaotra - Avaradrano</t>
+          <t>Avaradrano</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -1381,7 +1381,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Alaotra - Avaradrano</t>
+          <t>Avaradrano</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -1404,7 +1404,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Alaotra - Avaradrano</t>
+          <t>Avaradrano</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -1421,7 +1421,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Alaotra - Avaradrano</t>
+          <t>Avaradrano</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -1438,7 +1438,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Alaotra - Avaradrano</t>
+          <t>Avaradrano</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -1455,7 +1455,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Alaotra - Feramanga Atsimo</t>
+          <t>Feramanga Atsimo</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -1472,7 +1472,7 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Alaotra - Feramanga Atsimo</t>
+          <t>Feramanga Atsimo</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -1489,7 +1489,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Alaotra - Feramanga Atsimo</t>
+          <t>Feramanga Atsimo</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -1512,7 +1512,7 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Alaotra - Feramanga Atsimo</t>
+          <t>Feramanga Atsimo</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -1529,7 +1529,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Alaotra - Feramanga Atsimo</t>
+          <t>Feramanga Atsimo</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -1546,7 +1546,7 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Alaotra - Feramanga Atsimo</t>
+          <t>Feramanga Atsimo</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -1563,7 +1563,7 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Alaotra - Feramanga Atsimo</t>
+          <t>Feramanga Atsimo</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -1580,7 +1580,7 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Alaotra - Feramanga Atsimo</t>
+          <t>Feramanga Atsimo</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -1603,7 +1603,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Alaotra - Feramanga Atsimo</t>
+          <t>Feramanga Atsimo</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -1620,7 +1620,7 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Alaotra - Feramanga Atsimo</t>
+          <t>Feramanga Atsimo</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -1643,7 +1643,7 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Alaotra - Feramanga Atsimo</t>
+          <t>Feramanga Atsimo</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -1660,7 +1660,7 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Alaotra - Mangabe</t>
+          <t>Mangabe</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -1677,7 +1677,7 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Alaotra - Mangabe</t>
+          <t>Mangabe</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -1694,7 +1694,7 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Alaotra - Mangabe</t>
+          <t>Mangabe</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -1717,7 +1717,7 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Alaotra - Mangabe</t>
+          <t>Mangabe</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -1734,7 +1734,7 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Alaotra - Mangabe</t>
+          <t>Mangabe</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -1751,7 +1751,7 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Alaotra - Mangabe</t>
+          <t>Mangabe</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -1768,7 +1768,7 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Alaotra - Mangabe</t>
+          <t>Mangabe</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -1785,7 +1785,7 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Alaotra - Mangabe</t>
+          <t>Mangabe</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -1808,7 +1808,7 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Alaotra - Mangabe</t>
+          <t>Mangabe</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -1825,7 +1825,7 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Alaotra - Mangabe</t>
+          <t>Mangabe</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -1842,7 +1842,7 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Alaotra - Mangabe</t>
+          <t>Mangabe</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -1859,7 +1859,7 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Alaotra - Tous</t>
+          <t>Tous</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -1882,7 +1882,7 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Alaotra - Tous</t>
+          <t>Tous</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -1905,7 +1905,7 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Alaotra - Tous</t>
+          <t>Tous</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -1928,7 +1928,7 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Alaotra - Tous</t>
+          <t>Tous</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -1951,7 +1951,7 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Alaotra - Tous</t>
+          <t>Tous</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -1974,7 +1974,7 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Alaotra - Tous</t>
+          <t>Tous</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -1997,7 +1997,7 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Alaotra - Tous</t>
+          <t>Tous</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -2020,7 +2020,7 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Alaotra - Tous</t>
+          <t>Tous</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -2043,7 +2043,7 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Alaotra - Tous</t>
+          <t>Tous</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -2066,7 +2066,7 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Alaotra - Tous</t>
+          <t>Tous</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -2089,7 +2089,7 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Alaotra - Tous</t>
+          <t>Tous</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -2112,7 +2112,7 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Alaotra - Tous</t>
+          <t>Tous</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">

--- a/docs/downloads/04/tbl_cm_act_sex_alaotra_tous.xlsx
+++ b/docs/downloads/04/tbl_cm_act_sex_alaotra_tous.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E92"/>
+  <dimension ref="A1:E100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -508,7 +508,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Ouvrier agricole</t>
+          <t>Inactif / Retraité</t>
         </is>
       </c>
     </row>
@@ -525,7 +525,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Services &amp; Autres</t>
+          <t>Ouvrier agricole</t>
         </is>
       </c>
     </row>
@@ -537,19 +537,13 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Homme</t>
+          <t>Femme</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Artisanat, BTP &amp; Transport</t>
-        </is>
-      </c>
-      <c r="D10">
-        <v>13</v>
-      </c>
-      <c r="E10">
-        <v>23.2</v>
+          <t>Services &amp; Autres</t>
+        </is>
       </c>
     </row>
     <row r="11">
@@ -565,8 +559,14 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Commerce &amp; Restauration</t>
-        </is>
+          <t>Artisanat, BTP &amp; Transport</t>
+        </is>
+      </c>
+      <c r="D11">
+        <v>13</v>
+      </c>
+      <c r="E11">
+        <v>23.2</v>
       </c>
     </row>
     <row r="12">
@@ -582,14 +582,8 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Cultivateur exploitant</t>
-        </is>
-      </c>
-      <c r="D12">
-        <v>18</v>
-      </c>
-      <c r="E12">
-        <v>32.1</v>
+          <t>Commerce &amp; Restauration</t>
+        </is>
       </c>
     </row>
     <row r="13">
@@ -605,8 +599,14 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Elevage, Pêche &amp; Ress. nat.</t>
-        </is>
+          <t>Cultivateur exploitant</t>
+        </is>
+      </c>
+      <c r="D13">
+        <v>18</v>
+      </c>
+      <c r="E13">
+        <v>32.1</v>
       </c>
     </row>
     <row r="14">
@@ -622,14 +622,8 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Ouvrier agricole</t>
-        </is>
-      </c>
-      <c r="D14">
-        <v>16</v>
-      </c>
-      <c r="E14">
-        <v>28.6</v>
+          <t>Elevage, Pêche &amp; Ress. nat.</t>
+        </is>
       </c>
     </row>
     <row r="15">
@@ -645,47 +639,47 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Services &amp; Autres</t>
-        </is>
-      </c>
-      <c r="D15">
-        <v>5</v>
-      </c>
-      <c r="E15">
-        <v>8.9</v>
+          <t>Inactif / Retraité</t>
+        </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Ambodivoara</t>
+          <t>Ambatomanga</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Femme</t>
+          <t>Homme</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Artisanat, BTP &amp; Transport</t>
-        </is>
+          <t>Ouvrier agricole</t>
+        </is>
+      </c>
+      <c r="D16">
+        <v>16</v>
+      </c>
+      <c r="E16">
+        <v>28.6</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Ambodivoara</t>
+          <t>Ambatomanga</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Femme</t>
+          <t>Homme</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Commerce &amp; Restauration</t>
+          <t>Services &amp; Autres</t>
         </is>
       </c>
     </row>
@@ -702,14 +696,8 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Cultivateur exploitant</t>
-        </is>
-      </c>
-      <c r="D18">
-        <v>7</v>
-      </c>
-      <c r="E18">
-        <v>41.2</v>
+          <t>Artisanat, BTP &amp; Transport</t>
+        </is>
       </c>
     </row>
     <row r="19">
@@ -725,7 +713,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Ouvrier agricole</t>
+          <t>Commerce &amp; Restauration</t>
         </is>
       </c>
     </row>
@@ -742,8 +730,14 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Services &amp; Autres</t>
-        </is>
+          <t>Cultivateur exploitant</t>
+        </is>
+      </c>
+      <c r="D20">
+        <v>7</v>
+      </c>
+      <c r="E20">
+        <v>41.2</v>
       </c>
     </row>
     <row r="21">
@@ -754,12 +748,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Homme</t>
+          <t>Femme</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Artisanat, BTP &amp; Transport</t>
+          <t>Inactif / Retraité</t>
         </is>
       </c>
     </row>
@@ -771,12 +765,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Homme</t>
+          <t>Femme</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Commerce &amp; Restauration</t>
+          <t>Ouvrier agricole</t>
         </is>
       </c>
     </row>
@@ -793,14 +787,8 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Cultivateur exploitant</t>
-        </is>
-      </c>
-      <c r="D23">
-        <v>31</v>
-      </c>
-      <c r="E23">
-        <v>75.59999999999999</v>
+          <t>Artisanat, BTP &amp; Transport</t>
+        </is>
       </c>
     </row>
     <row r="24">
@@ -816,7 +804,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Elevage, Pêche &amp; Ress. nat.</t>
+          <t>Commerce &amp; Restauration</t>
         </is>
       </c>
     </row>
@@ -833,41 +821,47 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Ouvrier agricole</t>
-        </is>
+          <t>Cultivateur exploitant</t>
+        </is>
+      </c>
+      <c r="D25">
+        <v>31</v>
+      </c>
+      <c r="E25">
+        <v>75.59999999999999</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Ambohidrony</t>
+          <t>Ambodivoara</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Femme</t>
+          <t>Homme</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Artisanat, BTP &amp; Transport</t>
+          <t>Elevage, Pêche &amp; Ress. nat.</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Ambohidrony</t>
+          <t>Ambodivoara</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Femme</t>
+          <t>Homme</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Commerce &amp; Restauration</t>
+          <t>Ouvrier agricole</t>
         </is>
       </c>
     </row>
@@ -884,7 +878,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Cultivateur exploitant</t>
+          <t>Artisanat, BTP &amp; Transport</t>
         </is>
       </c>
     </row>
@@ -901,7 +895,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Elevage, Pêche &amp; Ress. nat.</t>
+          <t>Commerce &amp; Restauration</t>
         </is>
       </c>
     </row>
@@ -918,7 +912,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Ouvrier agricole</t>
+          <t>Cultivateur exploitant</t>
         </is>
       </c>
     </row>
@@ -935,7 +929,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Services &amp; Autres</t>
+          <t>Elevage, Pêche &amp; Ress. nat.</t>
         </is>
       </c>
     </row>
@@ -947,19 +941,13 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Homme</t>
+          <t>Femme</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Artisanat, BTP &amp; Transport</t>
-        </is>
-      </c>
-      <c r="D32">
-        <v>5</v>
-      </c>
-      <c r="E32">
-        <v>13.2</v>
+          <t>Inactif / Retraité</t>
+        </is>
       </c>
     </row>
     <row r="33">
@@ -970,12 +958,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Homme</t>
+          <t>Femme</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Commerce &amp; Restauration</t>
+          <t>Ouvrier agricole</t>
         </is>
       </c>
     </row>
@@ -987,19 +975,13 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Homme</t>
+          <t>Femme</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Cultivateur exploitant</t>
-        </is>
-      </c>
-      <c r="D34">
-        <v>16</v>
-      </c>
-      <c r="E34">
-        <v>42.1</v>
+          <t>Services &amp; Autres</t>
+        </is>
       </c>
     </row>
     <row r="35">
@@ -1015,7 +997,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Elevage, Pêche &amp; Ress. nat.</t>
+          <t>Artisanat, BTP &amp; Transport</t>
         </is>
       </c>
       <c r="D35">
@@ -1038,65 +1020,77 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Ouvrier agricole</t>
-        </is>
-      </c>
-      <c r="D36">
-        <v>11</v>
-      </c>
-      <c r="E36">
-        <v>28.9</v>
+          <t>Commerce &amp; Restauration</t>
+        </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Analamiranga</t>
+          <t>Ambohidrony</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Femme</t>
+          <t>Homme</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Artisanat, BTP &amp; Transport</t>
-        </is>
+          <t>Cultivateur exploitant</t>
+        </is>
+      </c>
+      <c r="D37">
+        <v>16</v>
+      </c>
+      <c r="E37">
+        <v>42.1</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Analamiranga</t>
+          <t>Ambohidrony</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Femme</t>
+          <t>Homme</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Commerce &amp; Restauration</t>
-        </is>
+          <t>Elevage, Pêche &amp; Ress. nat.</t>
+        </is>
+      </c>
+      <c r="D38">
+        <v>5</v>
+      </c>
+      <c r="E38">
+        <v>13.2</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Analamiranga</t>
+          <t>Ambohidrony</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Femme</t>
+          <t>Homme</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Cultivateur exploitant</t>
-        </is>
+          <t>Ouvrier agricole</t>
+        </is>
+      </c>
+      <c r="D39">
+        <v>11</v>
+      </c>
+      <c r="E39">
+        <v>28.9</v>
       </c>
     </row>
     <row r="40">
@@ -1112,7 +1106,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Ouvrier agricole</t>
+          <t>Artisanat, BTP &amp; Transport</t>
         </is>
       </c>
     </row>
@@ -1129,7 +1123,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Services &amp; Autres</t>
+          <t>Commerce &amp; Restauration</t>
         </is>
       </c>
     </row>
@@ -1141,12 +1135,12 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Homme</t>
+          <t>Femme</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Artisanat, BTP &amp; Transport</t>
+          <t>Cultivateur exploitant</t>
         </is>
       </c>
     </row>
@@ -1158,12 +1152,12 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Homme</t>
+          <t>Femme</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Commerce &amp; Restauration</t>
+          <t>Inactif / Retraité</t>
         </is>
       </c>
     </row>
@@ -1175,19 +1169,13 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Homme</t>
+          <t>Femme</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Cultivateur exploitant</t>
-        </is>
-      </c>
-      <c r="D44">
-        <v>26</v>
-      </c>
-      <c r="E44">
-        <v>72.2</v>
+          <t>Ouvrier agricole</t>
+        </is>
       </c>
     </row>
     <row r="45">
@@ -1198,19 +1186,13 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Homme</t>
+          <t>Femme</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Ouvrier agricole</t>
-        </is>
-      </c>
-      <c r="D45">
-        <v>5</v>
-      </c>
-      <c r="E45">
-        <v>13.9</v>
+          <t>Services &amp; Autres</t>
+        </is>
       </c>
     </row>
     <row r="46">
@@ -1226,81 +1208,87 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Services &amp; Autres</t>
+          <t>Artisanat, BTP &amp; Transport</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Avaradrano</t>
+          <t>Analamiranga</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Femme</t>
+          <t>Homme</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Artisanat, BTP &amp; Transport</t>
+          <t>Commerce &amp; Restauration</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Avaradrano</t>
+          <t>Analamiranga</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Femme</t>
+          <t>Homme</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Commerce &amp; Restauration</t>
-        </is>
+          <t>Cultivateur exploitant</t>
+        </is>
+      </c>
+      <c r="D48">
+        <v>26</v>
+      </c>
+      <c r="E48">
+        <v>72.2</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Avaradrano</t>
+          <t>Analamiranga</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Femme</t>
+          <t>Homme</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Cultivateur exploitant</t>
+          <t>Ouvrier agricole</t>
         </is>
       </c>
       <c r="D49">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="E49">
-        <v>61.9</v>
+        <v>13.9</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Avaradrano</t>
+          <t>Analamiranga</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Femme</t>
+          <t>Homme</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Elevage, Pêche &amp; Ress. nat.</t>
+          <t>Services &amp; Autres</t>
         </is>
       </c>
     </row>
@@ -1317,7 +1305,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Ouvrier agricole</t>
+          <t>Artisanat, BTP &amp; Transport</t>
         </is>
       </c>
     </row>
@@ -1334,7 +1322,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Services &amp; Autres</t>
+          <t>Commerce &amp; Restauration</t>
         </is>
       </c>
     </row>
@@ -1346,19 +1334,19 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Homme</t>
+          <t>Femme</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Artisanat, BTP &amp; Transport</t>
+          <t>Cultivateur exploitant</t>
         </is>
       </c>
       <c r="D53">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="E53">
-        <v>7.4</v>
+        <v>61.9</v>
       </c>
     </row>
     <row r="54">
@@ -1369,12 +1357,12 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Homme</t>
+          <t>Femme</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Commerce &amp; Restauration</t>
+          <t>Elevage, Pêche &amp; Ress. nat.</t>
         </is>
       </c>
     </row>
@@ -1386,19 +1374,13 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Homme</t>
+          <t>Femme</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Cultivateur exploitant</t>
-        </is>
-      </c>
-      <c r="D55">
-        <v>52</v>
-      </c>
-      <c r="E55">
-        <v>76.5</v>
+          <t>Inactif / Retraité</t>
+        </is>
       </c>
     </row>
     <row r="56">
@@ -1409,12 +1391,12 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Homme</t>
+          <t>Femme</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Elevage, Pêche &amp; Ress. nat.</t>
+          <t>Ouvrier agricole</t>
         </is>
       </c>
     </row>
@@ -1426,12 +1408,12 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Homme</t>
+          <t>Femme</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Ouvrier agricole</t>
+          <t>Services &amp; Autres</t>
         </is>
       </c>
     </row>
@@ -1448,93 +1430,99 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Services &amp; Autres</t>
-        </is>
+          <t>Artisanat, BTP &amp; Transport</t>
+        </is>
+      </c>
+      <c r="D58">
+        <v>5</v>
+      </c>
+      <c r="E58">
+        <v>7.4</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Feramanga Atsimo</t>
+          <t>Avaradrano</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Femme</t>
+          <t>Homme</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Artisanat, BTP &amp; Transport</t>
+          <t>Commerce &amp; Restauration</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Feramanga Atsimo</t>
+          <t>Avaradrano</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Femme</t>
+          <t>Homme</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Commerce &amp; Restauration</t>
-        </is>
+          <t>Cultivateur exploitant</t>
+        </is>
+      </c>
+      <c r="D60">
+        <v>52</v>
+      </c>
+      <c r="E60">
+        <v>76.5</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Feramanga Atsimo</t>
+          <t>Avaradrano</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Femme</t>
+          <t>Homme</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Cultivateur exploitant</t>
-        </is>
-      </c>
-      <c r="D61">
-        <v>7</v>
-      </c>
-      <c r="E61">
-        <v>46.7</v>
+          <t>Elevage, Pêche &amp; Ress. nat.</t>
+        </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Feramanga Atsimo</t>
+          <t>Avaradrano</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Femme</t>
+          <t>Homme</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Elevage, Pêche &amp; Ress. nat.</t>
+          <t>Inactif / Retraité</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Feramanga Atsimo</t>
+          <t>Avaradrano</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Femme</t>
+          <t>Homme</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -1546,7 +1534,7 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Feramanga Atsimo</t>
+          <t>Avaradrano</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -1556,7 +1544,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Artisanat, BTP &amp; Transport</t>
+          <t>Services &amp; Autres</t>
         </is>
       </c>
     </row>
@@ -1568,12 +1556,12 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Homme</t>
+          <t>Femme</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Commerce &amp; Restauration</t>
+          <t>Artisanat, BTP &amp; Transport</t>
         </is>
       </c>
     </row>
@@ -1585,19 +1573,13 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Homme</t>
+          <t>Femme</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Cultivateur exploitant</t>
-        </is>
-      </c>
-      <c r="D66">
-        <v>53</v>
-      </c>
-      <c r="E66">
-        <v>71.59999999999999</v>
+          <t>Commerce &amp; Restauration</t>
+        </is>
       </c>
     </row>
     <row r="67">
@@ -1608,13 +1590,19 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Homme</t>
+          <t>Femme</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Elevage, Pêche &amp; Ress. nat.</t>
-        </is>
+          <t>Cultivateur exploitant</t>
+        </is>
+      </c>
+      <c r="D67">
+        <v>7</v>
+      </c>
+      <c r="E67">
+        <v>46.7</v>
       </c>
     </row>
     <row r="68">
@@ -1625,19 +1613,13 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Homme</t>
+          <t>Femme</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Ouvrier agricole</t>
-        </is>
-      </c>
-      <c r="D68">
-        <v>9</v>
-      </c>
-      <c r="E68">
-        <v>12.2</v>
+          <t>Elevage, Pêche &amp; Ress. nat.</t>
+        </is>
       </c>
     </row>
     <row r="69">
@@ -1648,24 +1630,24 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Homme</t>
+          <t>Femme</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Services &amp; Autres</t>
+          <t>Ouvrier agricole</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Mangabe</t>
+          <t>Feramanga Atsimo</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Femme</t>
+          <t>Homme</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -1677,12 +1659,12 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Mangabe</t>
+          <t>Feramanga Atsimo</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Femme</t>
+          <t>Homme</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -1694,12 +1676,12 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Mangabe</t>
+          <t>Feramanga Atsimo</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Femme</t>
+          <t>Homme</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -1708,21 +1690,21 @@
         </is>
       </c>
       <c r="D72">
-        <v>10</v>
+        <v>53</v>
       </c>
       <c r="E72">
-        <v>52.6</v>
+        <v>71.59999999999999</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Mangabe</t>
+          <t>Feramanga Atsimo</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Femme</t>
+          <t>Homme</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -1734,29 +1716,35 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Mangabe</t>
+          <t>Feramanga Atsimo</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Femme</t>
+          <t>Homme</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
           <t>Ouvrier agricole</t>
         </is>
+      </c>
+      <c r="D74">
+        <v>9</v>
+      </c>
+      <c r="E74">
+        <v>12.2</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Mangabe</t>
+          <t>Feramanga Atsimo</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Femme</t>
+          <t>Homme</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -1773,7 +1761,7 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Homme</t>
+          <t>Femme</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -1790,19 +1778,13 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Homme</t>
+          <t>Femme</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Cultivateur exploitant</t>
-        </is>
-      </c>
-      <c r="D77">
-        <v>41</v>
-      </c>
-      <c r="E77">
-        <v>75.90000000000001</v>
+          <t>Commerce &amp; Restauration</t>
+        </is>
       </c>
     </row>
     <row r="78">
@@ -1813,13 +1795,19 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Homme</t>
+          <t>Femme</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Elevage, Pêche &amp; Ress. nat.</t>
-        </is>
+          <t>Cultivateur exploitant</t>
+        </is>
+      </c>
+      <c r="D78">
+        <v>10</v>
+      </c>
+      <c r="E78">
+        <v>52.6</v>
       </c>
     </row>
     <row r="79">
@@ -1830,12 +1818,12 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Homme</t>
+          <t>Femme</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Ouvrier agricole</t>
+          <t>Elevage, Pêche &amp; Ress. nat.</t>
         </is>
       </c>
     </row>
@@ -1847,19 +1835,19 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Homme</t>
+          <t>Femme</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Services &amp; Autres</t>
+          <t>Inactif / Retraité</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Tous</t>
+          <t>Mangabe</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -1869,48 +1857,36 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Artisanat, BTP &amp; Transport</t>
-        </is>
-      </c>
-      <c r="D81">
-        <v>8</v>
-      </c>
-      <c r="E81">
-        <v>7.3</v>
+          <t>Ouvrier agricole</t>
+        </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Tous</t>
+          <t>Mangabe</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Femme</t>
+          <t>Homme</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Commerce &amp; Restauration</t>
-        </is>
-      </c>
-      <c r="D82">
-        <v>18</v>
-      </c>
-      <c r="E82">
-        <v>16.5</v>
+          <t>Artisanat, BTP &amp; Transport</t>
+        </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Tous</t>
+          <t>Mangabe</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Femme</t>
+          <t>Homme</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -1919,79 +1895,61 @@
         </is>
       </c>
       <c r="D83">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="E83">
-        <v>42.2</v>
+        <v>75.90000000000001</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Tous</t>
+          <t>Mangabe</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Femme</t>
+          <t>Homme</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
           <t>Elevage, Pêche &amp; Ress. nat.</t>
         </is>
-      </c>
-      <c r="D84">
-        <v>6</v>
-      </c>
-      <c r="E84">
-        <v>5.5</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Tous</t>
+          <t>Mangabe</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Femme</t>
+          <t>Homme</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
           <t>Ouvrier agricole</t>
         </is>
-      </c>
-      <c r="D85">
-        <v>13</v>
-      </c>
-      <c r="E85">
-        <v>11.9</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Tous</t>
+          <t>Mangabe</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Femme</t>
+          <t>Homme</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
           <t>Services &amp; Autres</t>
         </is>
-      </c>
-      <c r="D86">
-        <v>18</v>
-      </c>
-      <c r="E86">
-        <v>16.5</v>
       </c>
     </row>
     <row r="87">
@@ -2002,7 +1960,7 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Homme</t>
+          <t>Femme</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
@@ -2011,10 +1969,10 @@
         </is>
       </c>
       <c r="D87">
-        <v>37</v>
+        <v>8</v>
       </c>
       <c r="E87">
-        <v>9.300000000000001</v>
+        <v>7.3</v>
       </c>
     </row>
     <row r="88">
@@ -2025,7 +1983,7 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Homme</t>
+          <t>Femme</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
@@ -2034,10 +1992,10 @@
         </is>
       </c>
       <c r="D88">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="E88">
-        <v>2.5</v>
+        <v>16.5</v>
       </c>
     </row>
     <row r="89">
@@ -2048,7 +2006,7 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Homme</t>
+          <t>Femme</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
@@ -2057,10 +2015,10 @@
         </is>
       </c>
       <c r="D89">
-        <v>259</v>
+        <v>46</v>
       </c>
       <c r="E89">
-        <v>65.40000000000001</v>
+        <v>42.2</v>
       </c>
     </row>
     <row r="90">
@@ -2071,7 +2029,7 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Homme</t>
+          <t>Femme</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
@@ -2080,10 +2038,10 @@
         </is>
       </c>
       <c r="D90">
-        <v>25</v>
+        <v>6</v>
       </c>
       <c r="E90">
-        <v>6.3</v>
+        <v>5.5</v>
       </c>
     </row>
     <row r="91">
@@ -2094,19 +2052,19 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Homme</t>
+          <t>Femme</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Ouvrier agricole</t>
+          <t>Inactif / Retraité</t>
         </is>
       </c>
       <c r="D91">
-        <v>50</v>
+        <v>12</v>
       </c>
       <c r="E91">
-        <v>12.6</v>
+        <v>11</v>
       </c>
     </row>
     <row r="92">
@@ -2117,19 +2075,197 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Homme</t>
+          <t>Femme</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
+          <t>Ouvrier agricole</t>
+        </is>
+      </c>
+      <c r="D92">
+        <v>13</v>
+      </c>
+      <c r="E92">
+        <v>11.9</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>Tous</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>Femme</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
           <t>Services &amp; Autres</t>
         </is>
       </c>
-      <c r="D92">
-        <v>15</v>
-      </c>
-      <c r="E92">
-        <v>3.8</v>
+      <c r="D93">
+        <v>6</v>
+      </c>
+      <c r="E93">
+        <v>5.5</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>Tous</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>Homme</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>Artisanat, BTP &amp; Transport</t>
+        </is>
+      </c>
+      <c r="D94">
+        <v>37</v>
+      </c>
+      <c r="E94">
+        <v>9.300000000000001</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>Tous</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>Homme</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>Commerce &amp; Restauration</t>
+        </is>
+      </c>
+      <c r="D95">
+        <v>10</v>
+      </c>
+      <c r="E95">
+        <v>2.5</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>Tous</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>Homme</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>Cultivateur exploitant</t>
+        </is>
+      </c>
+      <c r="D96">
+        <v>259</v>
+      </c>
+      <c r="E96">
+        <v>65.40000000000001</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>Tous</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>Homme</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>Elevage, Pêche &amp; Ress. nat.</t>
+        </is>
+      </c>
+      <c r="D97">
+        <v>25</v>
+      </c>
+      <c r="E97">
+        <v>6.3</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>Tous</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>Homme</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>Inactif / Retraité</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>Tous</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>Homme</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>Ouvrier agricole</t>
+        </is>
+      </c>
+      <c r="D99">
+        <v>50</v>
+      </c>
+      <c r="E99">
+        <v>12.6</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>Tous</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>Homme</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>Services &amp; Autres</t>
+        </is>
+      </c>
+      <c r="D100">
+        <v>11</v>
+      </c>
+      <c r="E100">
+        <v>2.8</v>
       </c>
     </row>
   </sheetData>
